--- a/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,65</t>
+          <t>3,15; 6,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,41</t>
+          <t>2,48; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,83</t>
+          <t>1,8; 4,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,49</t>
+          <t>3,01; 6,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,69</t>
+          <t>2,69; 5,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,71</t>
+          <t>2,47; 4,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,08</t>
+          <t>2,03; 4,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,41</t>
+          <t>1,89; 7,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,61</t>
+          <t>3,38; 5,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,17</t>
+          <t>2,68; 4,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,01</t>
+          <t>2,06; 4,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,23</t>
+          <t>2,8; 6,24</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,35</t>
+          <t>1,76; 3,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,5</t>
+          <t>2,39; 4,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,57</t>
+          <t>2,77; 5,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,48</t>
+          <t>3,53; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,99</t>
+          <t>2,92; 6,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,97</t>
+          <t>2,77; 5,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,51</t>
+          <t>2,32; 4,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,13</t>
+          <t>3,73; 7,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,46</t>
+          <t>2,51; 4,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,35</t>
+          <t>2,77; 4,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,61</t>
+          <t>2,78; 4,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,07</t>
+          <t>3,91; 6,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,44</t>
+          <t>2,73; 8,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,99</t>
+          <t>2,33; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,89</t>
+          <t>2,25; 6,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,14</t>
+          <t>3,11; 5,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,6</t>
+          <t>2,64; 5,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,56</t>
+          <t>1,63; 3,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,37</t>
+          <t>2,03; 4,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,33</t>
+          <t>3,69; 7,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,26</t>
+          <t>2,99; 6,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,96</t>
+          <t>2,29; 4,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,27</t>
+          <t>2,29; 4,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,88</t>
+          <t>3,69; 6,04</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,45</t>
+          <t>2,06; 4,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,7</t>
+          <t>2,51; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,92</t>
+          <t>1,93; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,93</t>
+          <t>2,99; 5,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,7</t>
+          <t>2,1; 6,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,9</t>
+          <t>2,99; 7,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,96</t>
+          <t>2,41; 7,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,31</t>
+          <t>4,38; 7,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,98</t>
+          <t>2,36; 5,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,21</t>
+          <t>3,16; 6,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,91</t>
+          <t>2,32; 5,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,05</t>
+          <t>4,11; 5,97</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,75</t>
+          <t>2,96; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,2</t>
+          <t>2,94; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,25</t>
+          <t>2,65; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,98</t>
+          <t>3,69; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,05</t>
+          <t>3,18; 4,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,39</t>
+          <t>2,98; 4,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,82</t>
+          <t>2,58; 4,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,12</t>
+          <t>4,42; 6,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,49</t>
+          <t>3,26; 4,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,04</t>
+          <t>3,08; 4,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,76</t>
+          <t>2,76; 3,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,35</t>
+          <t>4,24; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,65</t>
+          <t>3,13; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,51</t>
+          <t>2,49; 4,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,75</t>
+          <t>1,73; 4,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,62</t>
+          <t>2,89; 6,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,62</t>
+          <t>2,78; 5,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,67</t>
+          <t>2,54; 4,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,16</t>
+          <t>1,98; 4,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,42</t>
+          <t>1,91; 7,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,68</t>
+          <t>3,28; 5,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,19</t>
+          <t>2,73; 4,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,07</t>
+          <t>2,08; 4,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,24</t>
+          <t>2,93; 6,49</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,08</t>
+          <t>1,72; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,52</t>
+          <t>2,38; 4,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,33</t>
+          <t>2,78; 5,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,62</t>
+          <t>3,59; 5,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,06</t>
+          <t>2,87; 6,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,15</t>
+          <t>2,7; 4,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,71</t>
+          <t>2,35; 4,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,1</t>
+          <t>3,67; 7,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,52</t>
+          <t>2,6; 4,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,24</t>
+          <t>2,82; 4,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,51</t>
+          <t>2,78; 4,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,01</t>
+          <t>3,9; 6,06</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,52</t>
+          <t>2,65; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,9</t>
+          <t>2,35; 4,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,53</t>
+          <t>2,18; 6,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,85</t>
+          <t>3,11; 6,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,82</t>
+          <t>2,6; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,44</t>
+          <t>1,63; 3,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,48</t>
+          <t>2,02; 4,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,24</t>
+          <t>3,59; 7,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,25</t>
+          <t>3,17; 6,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,09</t>
+          <t>2,23; 3,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,53</t>
+          <t>2,36; 4,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,04</t>
+          <t>3,8; 6,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,57</t>
+          <t>2,04; 4,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,11</t>
+          <t>2,54; 7,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,03</t>
+          <t>1,88; 4,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,15</t>
+          <t>3,04; 5,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,91</t>
+          <t>2,1; 6,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,04</t>
+          <t>3,14; 7,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,55</t>
+          <t>2,08; 7,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,11</t>
+          <t>4,29; 7,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,12</t>
+          <t>2,37; 5,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,1</t>
+          <t>3,25; 6,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,08</t>
+          <t>2,33; 5,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,97</t>
+          <t>4,05; 6,06</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,68</t>
+          <t>2,83; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,17</t>
+          <t>2,89; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,23</t>
+          <t>2,67; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,95</t>
+          <t>3,67; 4,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,91</t>
+          <t>3,22; 4,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,42</t>
+          <t>2,97; 4,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,0</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,1</t>
+          <t>4,36; 6,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,46</t>
+          <t>3,29; 4,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,07</t>
+          <t>3,12; 4,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,84</t>
+          <t>2,76; 3,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,38</t>
+          <t>4,24; 5,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,79</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,38</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,58</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,66</t>
+          <t>2,8; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,53</t>
+          <t>2,48; 4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,5</t>
+          <t>1,96; 4,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,7</t>
+          <t>1,85; 7,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,67</t>
+          <t>2,99; 6,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,83</t>
+          <t>2,39; 4,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,19</t>
+          <t>1,82; 4,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,38</t>
+          <t>2,96; 6,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,57</t>
+          <t>3,27; 5,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,33</t>
+          <t>2,64; 4,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,09</t>
+          <t>2,09; 4,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,49</t>
+          <t>2,82; 6,18</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,0</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,22</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,63</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,26</t>
+          <t>2,84; 5,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,5</t>
+          <t>2,73; 4,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,57</t>
+          <t>2,36; 4,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,61</t>
+          <t>3,6; 7,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,25</t>
+          <t>1,73; 3,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,77</t>
+          <t>2,43; 4,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,54</t>
+          <t>2,8; 5,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,0</t>
+          <t>3,35; 5,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,58</t>
+          <t>2,57; 4,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,34</t>
+          <t>2,77; 4,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,53</t>
+          <t>2,8; 4,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,06</t>
+          <t>3,9; 6,03</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,45</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,37</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,64</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,81</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,22</t>
+          <t>2,61; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,89</t>
+          <t>1,63; 3,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,41</t>
+          <t>2,01; 4,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,09</t>
+          <t>3,82; 7,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,42</t>
+          <t>2,62; 8,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,56</t>
+          <t>2,32; 4,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,19</t>
+          <t>2,23; 6,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,47</t>
+          <t>3,13; 5,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,51</t>
+          <t>3,01; 6,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,92</t>
+          <t>2,29; 3,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,42</t>
+          <t>2,25; 4,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,15</t>
+          <t>3,77; 5,99</t>
         </is>
       </c>
     </row>
@@ -1068,44 +1068,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,61</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,67</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,07</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,24</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,55</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3,91</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,65</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,59</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3,36</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,98</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,66</t>
+          <t>2,01; 6,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,61</t>
+          <t>3,13; 6,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,09</t>
+          <t>2,11; 6,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,01</t>
+          <t>4,5; 7,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,7</t>
+          <t>1,95; 4,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,09</t>
+          <t>2,52; 7,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,13</t>
+          <t>1,84; 3,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,08</t>
+          <t>2,88; 5,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,12</t>
+          <t>2,35; 4,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,25</t>
+          <t>3,26; 6,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,02</t>
+          <t>2,32; 4,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,06</t>
+          <t>4,13; 6,06</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,46</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,26</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,8</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,75</t>
+          <t>3,22; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,18</t>
+          <t>2,99; 4,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,15</t>
+          <t>2,54; 3,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,92</t>
+          <t>4,49; 6,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,91</t>
+          <t>2,94; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,38</t>
+          <t>2,87; 4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,65; 4,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,11</t>
+          <t>3,63; 4,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,23; 4,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,04</t>
+          <t>3,11; 4,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,83</t>
+          <t>2,77; 3,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,41</t>
+          <t>4,25; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que los menores limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,67</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.246856148584297</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.308677158440888</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.822851915027045</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.791517167874134</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>4.671622574794298</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3.380802413776043</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.704584710494772</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>4.615961794359616</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4.46471598395065</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3.348940516948181</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.747439125656195</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>4.187605547986951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,8; 5,69</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,48; 4,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,96; 4,08</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 7,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 6,65</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,39; 4,41</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,82; 4,83</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 6,51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3,27; 5,61</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2,64; 4,17</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2,09; 4,01</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,82; 6,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.80213419442294</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.478524449068559</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.95660004601945</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.848896913834769</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2.989252622114403</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>2.385207253350172</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.819239611035358</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.963674944826812</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>3.272959310753314</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.642647099358888</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>2.0858444916908</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>2.820398997119106</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.692600209055716</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.708413435317633</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.084669480637954</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.506307840159836</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.648954469735979</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.414410717334571</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4.825064462533195</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.514532663009252</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>5.606279386330915</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>4.166736672249692</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>4.012877904052225</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>6.175129480862575</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,63</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,73</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,84; 5,99</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,73; 4,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,36; 4,51</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 7,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 3,35</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,43; 4,5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,8; 5,57</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3,35; 5,36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2,57; 4,46</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2,77; 4,35</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2,8; 4,61</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 6,03</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.106972765283456</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.595928715780417</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.147084409318441</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.997094574965415</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.320531400563406</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3.223379195982544</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>3.626674509596629</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>4.437369386029673</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>3.340863985854451</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>3.429679132278312</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>3.412171937661034</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>4.733750715381261</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,16</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4,37</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2.844823086391917</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2.734854565907072</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.361255333854755</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>3.600087664662384</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.731847370561179</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2.428833961176828</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2.799795416789993</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>3.346103424091252</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2.57144865367514</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2.773722070812387</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>2.79639840379061</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>3.902532284266216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,61; 5,6</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 3,56</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,01; 4,37</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,82; 7,47</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,62; 8,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,32; 4,99</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 6,89</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 5,91</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>3,01; 6,26</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2,29; 3,96</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2,25; 4,27</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,77; 5,99</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.992911922340464</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.972824753562042</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.50817496878646</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.16580853718155</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3.349097754220165</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>4.501795548330147</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.567017835577204</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>5.358700273525899</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>4.457964572546009</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>4.347259876592576</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>4.610753713369076</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>6.02594507349607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,19</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,24</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,91</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4,47</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.599729850301755</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.355857125777345</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.703824432790391</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.445599649097748</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.133504934511796</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3.374385198684876</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3.636588725534816</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4.156669921731552</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>4.372070086434401</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2.949292728767954</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3.123040601229692</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>4.808740406604944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,01; 6,7</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 6,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,11; 6,96</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,5; 7,35</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 4,45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,52; 7,7</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,84; 3,92</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2,88; 5,0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,35; 4,98</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3,26; 6,21</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2,32; 4,91</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,13; 6,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2.608276673309916</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.627627016184219</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.009492310420448</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3.815590169619876</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2.618080567282193</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2.322506308594008</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2.228055172742919</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>3.134053071246665</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>3.013731653137297</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>2.292605058744531</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>2.250661505096311</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.76692424953042</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.595734420828296</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.561753068289307</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.367305999464196</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.468563257847103</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.444389615897721</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.987413176277166</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>6.886182971691376</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>5.911679526662186</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.261667687070095</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>3.964843936884866</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>4.271917495079819</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>5.988724431748334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.648985088299646</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.610089525243102</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.190683850538691</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5.665440721854911</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3.073157794166101</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>4.238912721928763</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2.549208678564154</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>3.9065022096007</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>3.358302849127675</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>4.470102689960847</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>3.315659048365869</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>4.98172760503912</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2.007269660027781</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3.127933979303675</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.114081300783385</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4.502408701723226</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.954165198921122</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>2.521535144309094</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.84447512337999</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2.879998612093543</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>2.35326047417051</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>3.256131701225384</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>2.316682729259179</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>4.130951815668664</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.702522296873121</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.904806104758384</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.964991336886646</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.349353121864737</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>4.452339453562947</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.698377739047825</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3.917209543138854</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>4.998227798561701</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>4.980460876255682</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>6.21111418188948</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>4.910411822056216</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>6.057194096248798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,22; 5,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 4,39</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2,54; 3,82</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 6,23</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,94; 4,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 4,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,65; 4,25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,63; 4,9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3,23; 4,49</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3,11; 4,04</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2,77; 3,76</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 5,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.945601916730845</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.588834497697063</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.133645839672639</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.2883898255871</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.656725791927583</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.456844234535392</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3.264182514215749</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>4.196507506838844</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>3.807920160023901</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>3.524737585550751</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>3.20405118490479</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>4.799125101621544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3.216835100523757</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2.98630270680005</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2.537059761609317</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4.491646449014863</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.93737531074011</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2.872547917331249</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.654237545863394</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>3.630459632788607</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.232162117499079</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>3.106832931488398</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>2.766593329066177</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>4.251364057267459</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.051663667690388</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.394134864994804</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.816646597527908</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.234195483667308</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.747348062115237</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>4.197378411003905</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>4.248348263941926</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>4.903035894506758</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>4.487814821461741</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.039193618632256</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>3.75975515804398</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>5.378420792859535</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
